--- a/output/pdf_financials_xlsx/FMAN.xlsx
+++ b/output/pdf_financials_xlsx/FMAN.xlsx
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.028286</v>
+        <v>-0.028286</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.11656</v>
+        <v>-0.11656</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-3.48983</v>
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.028286</v>
+        <v>-0.028286</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.11656</v>
+        <v>-0.11656</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-3.48983</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.028286</v>
+        <v>-0.028286</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.11656</v>
+        <v>-0.11656</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-3.48983</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-0.188573</v>
+        <v>0.188573</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-3.885333</v>
+        <v>3.885333</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>84.34858199999999</v>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.028286</v>
+        <v>-0.028286</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.11656</v>
+        <v>-0.11656</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-3.48983</v>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.028286</v>
+        <v>-0.028286</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.11656</v>
+        <v>-0.11656</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-3.48983</v>
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -3053,22 +3053,22 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.047447</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.36948</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.99095</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.24509</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.40678</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.601711</v>
       </c>
     </row>
     <row r="93">
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>-2.573381</v>
+        <v>-2.486351</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>-12.488098</v>
@@ -5100,7 +5100,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -5841,7 +5845,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -6526,7 +6534,11 @@
           <t>Reserve 7</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -9601,7 +9613,11 @@
           <t>Depreciation of property, plant and equipment included in exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -14515,10 +14531,10 @@
         </is>
       </c>
       <c r="E204" s="5" t="n">
-        <v>0.028286</v>
+        <v>-0.028286</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>0.11656</v>
+        <v>-0.11656</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FMAN.xlsx
+++ b/output/pdf_financials_xlsx/FMAN.xlsx
@@ -738,10 +738,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.06858499999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.129299</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1196,10 +1196,10 @@
         <v>-3.48983</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.671109</v>
+        <v>-1.739694</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.671109</v>
+        <v>-1.800408</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.032242</v>
@@ -1252,10 +1252,10 @@
         <v>-3.48983</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.671109</v>
+        <v>-1.739694</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.671109</v>
+        <v>-1.800408</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.032242</v>
@@ -1390,13 +1390,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.093097</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.61383</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>20.054776</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>5.311644</v>
@@ -1446,13 +1446,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.093097</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.61383</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>20.054776</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>5.311644</v>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.09841</v>
+        <v>0.005313</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.61383</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>20.124218</v>
+        <v>0.069442</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.08111</v>
@@ -3934,13 +3934,13 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.043994</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.07887</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.032862</v>
       </c>
       <c r="H124" s="3" t="n">
         <v>0</v>
@@ -3962,13 +3962,13 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.043994</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.07887</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.032862</v>
       </c>
       <c r="H125" s="3" t="n">
         <v>0</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
@@ -7877,7 +7877,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -12699,7 +12703,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">

--- a/output/pdf_financials_xlsx/FMAN.xlsx
+++ b/output/pdf_financials_xlsx/FMAN.xlsx
@@ -604,7 +604,7 @@
         <v>0.002621</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.002142</v>
+        <v>0.08214200000000001</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.002962</v>
@@ -688,7 +688,7 @@
         <v>1.029433</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.024878</v>
+        <v>1.104878</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>1.748198</v>
@@ -2247,22 +2247,22 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.06786300000000001</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.382173</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.36884</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.10839</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.006437</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.310552</v>
       </c>
     </row>
     <row r="65">
@@ -2328,25 +2328,25 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.021446</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.006932</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.022899</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.081926</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.3375</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.369201</v>
       </c>
     </row>
     <row r="68">
@@ -3284,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004203</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0.068813</v>
@@ -3424,7 +3424,7 @@
         <v>0.016133</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.057269</v>
+        <v>0.053066</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.154651</v>
@@ -9827,7 +9827,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -10590,7 +10594,11 @@
           <t>Director Fees</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -12205,7 +12213,11 @@
           <t>Director fees 6</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
